--- a/diseases/d132/2015-2019.xlsx
+++ b/diseases/d132/2015-2019.xlsx
@@ -16165,6 +16165,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16902,6 +16907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17639,6 +17649,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18524,6 +18539,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19261,6 +19281,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19998,6 +20023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20883,6 +20913,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21620,6 +21655,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22505,6 +22545,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23242,6 +23287,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23979,6 +24029,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24864,6 +24919,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25601,6 +25661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26338,6 +26403,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27075,6 +27145,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27960,6 +28035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28697,6 +28777,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29582,6 +29667,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30319,6 +30409,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31056,6 +31151,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31941,6 +32041,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32678,6 +32783,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33415,6 +33525,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34300,6 +34415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35037,6 +35157,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35922,6 +36047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36659,6 +36789,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37396,6 +37531,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38133,6 +38273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39018,6 +39163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39755,6 +39905,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40492,6 +40647,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41377,6 +41537,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42114,6 +42279,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42999,6 +43169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43734,6 +43909,11 @@
       <c r="S293" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO293" t="inlineStr">
